--- a/pump_list.xlsx
+++ b/pump_list.xlsx
@@ -1,45 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8CD41BF-44C5-4F52-90CA-63A153A5F641}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="Polaris WebOffice" lastEdited="7" lowestEdited="7" rupBuild=""/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E959A26E-388F-4BF6-BDA7-5A8DA0DD4EBE}"/>
+    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="db" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="91">
   <si>
     <t>Song Title</t>
   </si>
@@ -306,76 +282,380 @@
   </si>
   <si>
     <t>Cross+Revolution (feat. LyuU)</t>
+  </si>
+  <si>
+    <t>DP_1</t>
+  </si>
+  <si>
+    <t>CO_1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="23">
     <font>
-      <sz val="11"/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
+      <sz val="8.0"/>
       <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
       <scheme val="minor"/>
+      <color rgb="FF000000"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
       <color rgb="FFFFFFFF"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
       <color rgb="FFCC0000"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11.0"/>
       <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
       <scheme val="minor"/>
+      <color theme="10"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="11"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FFFF0000"/>
+    </font>
+    <font>
+      <sz val="18.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="3"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF3F3F76"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF3F3F3F"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FFFA7D00"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FFFA7D00"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="1"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF006100"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF9C0006"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF9C6500"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="0"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF7F7F7F"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="gray125">
+        <fgColor rgb="FF000000"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2D3436"/>
-        <bgColor indexed="64"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="11">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -390,11 +670,261 @@
       <bottom style="medium">
         <color rgb="FFDDDDDD"/>
       </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FFACCCEA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.399980"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="7" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="5" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="0" applyFont="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="8" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="32" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -402,29 +932,67 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
+    <cellStyle name="20% - 강조색1" xfId="25" builtinId="30"/>
+    <cellStyle name="20% - 강조색2" xfId="29" builtinId="34"/>
+    <cellStyle name="20% - 강조색3" xfId="33" builtinId="38"/>
+    <cellStyle name="20% - 강조색4" xfId="37" builtinId="42"/>
+    <cellStyle name="20% - 강조색5" xfId="41" builtinId="46"/>
+    <cellStyle name="20% - 강조색6" xfId="45" builtinId="50"/>
+    <cellStyle name="40% - 강조색1" xfId="26" builtinId="31"/>
+    <cellStyle name="40% - 강조색2" xfId="30" builtinId="35"/>
+    <cellStyle name="40% - 강조색3" xfId="34" builtinId="39"/>
+    <cellStyle name="40% - 강조색4" xfId="38" builtinId="43"/>
+    <cellStyle name="40% - 강조색5" xfId="42" builtinId="47"/>
+    <cellStyle name="40% - 강조색6" xfId="46" builtinId="51"/>
+    <cellStyle name="60% - 강조색1" xfId="27" builtinId="32"/>
+    <cellStyle name="60% - 강조색2" xfId="31" builtinId="36"/>
+    <cellStyle name="60% - 강조색3" xfId="35" builtinId="40"/>
+    <cellStyle name="60% - 강조색4" xfId="39" builtinId="44"/>
+    <cellStyle name="60% - 강조색5" xfId="43" builtinId="48"/>
+    <cellStyle name="60% - 강조색6" xfId="47" builtinId="52"/>
+    <cellStyle name="강조색1" xfId="24" builtinId="29"/>
+    <cellStyle name="강조색2" xfId="28" builtinId="33"/>
+    <cellStyle name="강조색3" xfId="32" builtinId="37"/>
+    <cellStyle name="강조색4" xfId="36" builtinId="41"/>
+    <cellStyle name="강조색5" xfId="40" builtinId="45"/>
+    <cellStyle name="강조색6" xfId="44" builtinId="49"/>
+    <cellStyle name="경고문" xfId="9" builtinId="11"/>
+    <cellStyle name="계산" xfId="17" builtinId="22"/>
+    <cellStyle name="나쁨" xfId="22" builtinId="27"/>
+    <cellStyle name="메모" xfId="8" builtinId="10"/>
+    <cellStyle name="백분율" xfId="3" builtinId="5"/>
+    <cellStyle name="보통" xfId="23" builtinId="28"/>
+    <cellStyle name="설명텍스트" xfId="48" builtinId="53"/>
+    <cellStyle name="셀 확인" xfId="18" builtinId="23"/>
+    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
+    <cellStyle name="쉼표[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="연결된 셀" xfId="19" builtinId="24"/>
+    <cellStyle name="열어본 하이퍼링크" xfId="7" builtinId="9" hidden="1"/>
+    <cellStyle name="요약" xfId="20" builtinId="25"/>
+    <cellStyle name="입력" xfId="15" builtinId="20"/>
+    <cellStyle name="제목" xfId="10" builtinId="15"/>
+    <cellStyle name="제목1" xfId="11" builtinId="16"/>
+    <cellStyle name="제목2" xfId="12" builtinId="17"/>
+    <cellStyle name="제목3" xfId="13" builtinId="18"/>
+    <cellStyle name="제목4" xfId="14" builtinId="19"/>
+    <cellStyle name="좋음" xfId="21" builtinId="26"/>
+    <cellStyle name="출력" xfId="16" builtinId="21"/>
+    <cellStyle name="통화" xfId="2" builtinId="4"/>
+    <cellStyle name="통화[0]" xfId="5" builtinId="7"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="6" builtinId="8" hidden="1"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -744,19 +1312,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C92A4E16-3CC7-4F9A-8297-866C7D367EF2}">
-  <dimension ref="A1:S32"/>
-  <sheetFormatPr defaultColWidth="58" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:U32"/>
+  <sheetFormatPr defaultColWidth="58.00000000" defaultRowHeight="16.500000"/>
   <cols>
-    <col min="1" max="1" width="30.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.75" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="40.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="36.75" bestFit="1" customWidth="1"/>
-    <col min="6" max="19" width="4.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.37999916" customWidth="1" outlineLevel="0"/>
+    <col min="2" max="2" width="10.00500011" customWidth="1" outlineLevel="0"/>
+    <col min="3" max="3" width="13.75500011" customWidth="1" outlineLevel="0"/>
+    <col min="4" max="4" width="40.50500107" customWidth="1" outlineLevel="0"/>
+    <col min="5" max="5" width="36.75500107" customWidth="1" outlineLevel="0"/>
+    <col min="6" max="19" width="4.63000011" customWidth="1" outlineLevel="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:21" ht="17.250000">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -814,8 +1382,14 @@
       <c r="S1" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="2" spans="1:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="T1" s="0" t="s">
+        <v>89</v>
+      </c>
+      <c r="U1" s="0" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" ht="17.250000">
       <c r="A2" s="2" t="s">
         <v>20</v>
       </c>
@@ -831,22 +1405,50 @@
       <c r="E2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3"/>
-      <c r="P2" s="3"/>
+      <c r="F2" s="3">
+        <v>2</v>
+      </c>
+      <c r="G2" s="3">
+        <v>4</v>
+      </c>
+      <c r="H2" s="3">
+        <v>6</v>
+      </c>
+      <c r="I2" s="3">
+        <v>9</v>
+      </c>
+      <c r="J2" s="3">
+        <v>15</v>
+      </c>
+      <c r="K2" s="3">
+        <v>18</v>
+      </c>
+      <c r="L2" s="3">
+        <v>21</v>
+      </c>
+      <c r="M2" s="3">
+        <v>15</v>
+      </c>
+      <c r="N2" s="3">
+        <v>18</v>
+      </c>
+      <c r="O2" s="3">
+        <v>21</v>
+      </c>
+      <c r="P2" s="3">
+        <v>23</v>
+      </c>
       <c r="Q2" s="3"/>
       <c r="R2" s="3"/>
       <c r="S2" s="3"/>
-    </row>
-    <row r="3" spans="1:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="T2" s="0">
+        <v>3</v>
+      </c>
+      <c r="U2" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" ht="17.250000">
       <c r="A3" s="2" t="s">
         <v>20</v>
       </c>
@@ -862,22 +1464,40 @@
       <c r="E3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
+      <c r="F3" s="3">
+        <v>1</v>
+      </c>
+      <c r="G3" s="3">
+        <v>3</v>
+      </c>
+      <c r="H3" s="3">
+        <v>6</v>
+      </c>
+      <c r="I3" s="3">
+        <v>9</v>
+      </c>
+      <c r="J3" s="3">
+        <v>15</v>
+      </c>
+      <c r="K3" s="3">
+        <v>19</v>
+      </c>
       <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
+      <c r="M3" s="3">
+        <v>13</v>
+      </c>
+      <c r="N3" s="3">
+        <v>17</v>
+      </c>
+      <c r="O3" s="3">
+        <v>21</v>
+      </c>
       <c r="P3" s="3"/>
       <c r="Q3" s="3"/>
       <c r="R3" s="3"/>
       <c r="S3" s="3"/>
     </row>
-    <row r="4" spans="1:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:21" ht="17.250000">
       <c r="A4" s="2" t="s">
         <v>20</v>
       </c>
@@ -893,22 +1513,40 @@
       <c r="E4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
+      <c r="F4" s="3">
+        <v>1</v>
+      </c>
+      <c r="G4" s="3">
+        <v>3</v>
+      </c>
+      <c r="H4" s="3">
+        <v>6</v>
+      </c>
+      <c r="I4" s="3">
+        <v>9</v>
+      </c>
+      <c r="J4" s="3">
+        <v>15</v>
+      </c>
+      <c r="K4" s="3">
+        <v>17</v>
+      </c>
       <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="3"/>
+      <c r="M4" s="3">
+        <v>15</v>
+      </c>
+      <c r="N4" s="3">
+        <v>19</v>
+      </c>
+      <c r="O4" s="3">
+        <v>21</v>
+      </c>
       <c r="P4" s="3"/>
       <c r="Q4" s="3"/>
       <c r="R4" s="3"/>
       <c r="S4" s="3"/>
     </row>
-    <row r="5" spans="1:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:21" ht="17.250000">
       <c r="A5" s="2" t="s">
         <v>20</v>
       </c>
@@ -922,14 +1560,18 @@
       <c r="E5" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="F5" s="3"/>
+      <c r="F5" s="3">
+        <v>26</v>
+      </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
+      <c r="M5" s="3">
+        <v>29</v>
+      </c>
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
       <c r="P5" s="3"/>
@@ -937,7 +1579,7 @@
       <c r="R5" s="3"/>
       <c r="S5" s="3"/>
     </row>
-    <row r="6" spans="1:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:21" ht="17.250000">
       <c r="A6" s="2" t="s">
         <v>20</v>
       </c>
@@ -953,14 +1595,18 @@
       <c r="E6" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="3"/>
+      <c r="F6" s="3">
+        <v>22</v>
+      </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
+      <c r="M6" s="3">
+        <v>26</v>
+      </c>
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
       <c r="P6" s="3"/>
@@ -968,7 +1614,7 @@
       <c r="R6" s="3"/>
       <c r="S6" s="3"/>
     </row>
-    <row r="7" spans="1:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:21" ht="17.250000">
       <c r="A7" s="2" t="s">
         <v>20</v>
       </c>
@@ -991,7 +1637,9 @@
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
+      <c r="M7" s="3">
+        <v>23</v>
+      </c>
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
       <c r="P7" s="3"/>
@@ -999,7 +1647,7 @@
       <c r="R7" s="3"/>
       <c r="S7" s="3"/>
     </row>
-    <row r="8" spans="1:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:21" ht="17.250000">
       <c r="A8" s="2" t="s">
         <v>20</v>
       </c>
@@ -1013,22 +1661,28 @@
       <c r="E8" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F8" s="3"/>
+      <c r="F8" s="3">
+        <v>23</v>
+      </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
+      <c r="M8" s="3">
+        <v>23</v>
+      </c>
+      <c r="N8" s="3">
+        <v>25</v>
+      </c>
       <c r="O8" s="3"/>
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
       <c r="S8" s="3"/>
     </row>
-    <row r="9" spans="1:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:21" ht="17.250000">
       <c r="A9" s="2" t="s">
         <v>20</v>
       </c>
@@ -1042,22 +1696,32 @@
       <c r="E9" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F9" s="3"/>
+      <c r="F9" s="3">
+        <v>25</v>
+      </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="3"/>
-      <c r="P9" s="3"/>
+      <c r="M9" s="3">
+        <v>27</v>
+      </c>
+      <c r="N9" s="3">
+        <v>30</v>
+      </c>
+      <c r="O9" s="3">
+        <v>31</v>
+      </c>
+      <c r="P9" s="3">
+        <v>33</v>
+      </c>
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
       <c r="S9" s="3"/>
     </row>
-    <row r="10" spans="1:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:21" ht="17.250000">
       <c r="A10" s="2" t="s">
         <v>20</v>
       </c>
@@ -1071,14 +1735,18 @@
       <c r="E10" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F10" s="3"/>
+      <c r="F10" s="3">
+        <v>19</v>
+      </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
+      <c r="M10" s="3">
+        <v>21</v>
+      </c>
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
@@ -1086,7 +1754,7 @@
       <c r="R10" s="3"/>
       <c r="S10" s="3"/>
     </row>
-    <row r="11" spans="1:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:21" ht="17.250000">
       <c r="A11" s="2" t="s">
         <v>20</v>
       </c>
@@ -1109,7 +1777,9 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
+      <c r="M11" s="3">
+        <v>20</v>
+      </c>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
@@ -1117,7 +1787,7 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
     </row>
-    <row r="12" spans="1:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:21" ht="17.250000">
       <c r="A12" s="2" t="s">
         <v>20</v>
       </c>
@@ -1131,14 +1801,18 @@
       <c r="E12" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="F12" s="3"/>
+      <c r="F12" s="3">
+        <v>21</v>
+      </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
+      <c r="M12" s="3">
+        <v>26</v>
+      </c>
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
@@ -1146,7 +1820,7 @@
       <c r="R12" s="3"/>
       <c r="S12" s="3"/>
     </row>
-    <row r="13" spans="1:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:21" ht="17.250000">
       <c r="A13" s="2" t="s">
         <v>20</v>
       </c>
@@ -1167,7 +1841,9 @@
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
+      <c r="M13" s="3">
+        <v>23</v>
+      </c>
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
@@ -1175,7 +1851,7 @@
       <c r="R13" s="3"/>
       <c r="S13" s="3"/>
     </row>
-    <row r="14" spans="1:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:21" ht="17.250000">
       <c r="A14" s="2" t="s">
         <v>20</v>
       </c>
@@ -1198,15 +1874,19 @@
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
-      <c r="N14" s="3"/>
+      <c r="M14" s="3">
+        <v>29</v>
+      </c>
+      <c r="N14" s="3">
+        <v>31</v>
+      </c>
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
       <c r="R14" s="3"/>
       <c r="S14" s="3"/>
     </row>
-    <row r="15" spans="1:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:21" ht="17.250000">
       <c r="A15" s="2" t="s">
         <v>20</v>
       </c>
@@ -1222,22 +1902,34 @@
       <c r="E15" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
+      <c r="F15" s="3">
+        <v>14</v>
+      </c>
+      <c r="G15" s="3">
+        <v>17</v>
+      </c>
+      <c r="H15" s="3">
+        <v>19</v>
+      </c>
+      <c r="I15" s="3">
+        <v>22</v>
+      </c>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
-      <c r="N15" s="3"/>
+      <c r="M15" s="3">
+        <v>19</v>
+      </c>
+      <c r="N15" s="3">
+        <v>23</v>
+      </c>
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
       <c r="Q15" s="3"/>
       <c r="R15" s="3"/>
       <c r="S15" s="3"/>
     </row>
-    <row r="16" spans="1:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:21" ht="17.250000">
       <c r="A16" s="2" t="s">
         <v>20</v>
       </c>
@@ -1251,14 +1943,18 @@
       <c r="E16" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="3"/>
+      <c r="F16" s="3">
+        <v>22</v>
+      </c>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-      <c r="M16" s="3"/>
+      <c r="M16" s="3">
+        <v>23</v>
+      </c>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
@@ -1266,19 +1962,21 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
     </row>
-    <row r="17" spans="1:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:19" ht="17.250000">
       <c r="A17" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C17" s="2"/>
+        <v>5</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="D17" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
@@ -1287,7 +1985,9 @@
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
-      <c r="M17" s="3"/>
+      <c r="M17" s="3">
+        <v>22</v>
+      </c>
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
       <c r="P17" s="3"/>
@@ -1295,21 +1995,21 @@
       <c r="R17" s="3"/>
       <c r="S17" s="3"/>
     </row>
-    <row r="18" spans="1:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:19" ht="17.250000">
       <c r="A18" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
@@ -1318,7 +2018,9 @@
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
-      <c r="M18" s="3"/>
+      <c r="M18" s="3">
+        <v>21</v>
+      </c>
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
@@ -1326,7 +2028,7 @@
       <c r="R18" s="3"/>
       <c r="S18" s="3"/>
     </row>
-    <row r="19" spans="1:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:19" ht="17.250000">
       <c r="A19" s="2" t="s">
         <v>20</v>
       </c>
@@ -1337,10 +2039,10 @@
         <v>22</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
@@ -1349,7 +2051,9 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-      <c r="M19" s="3"/>
+      <c r="M19" s="3">
+        <v>25</v>
+      </c>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
@@ -1357,7 +2061,7 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
     </row>
-    <row r="20" spans="1:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:19" ht="17.250000">
       <c r="A20" s="2" t="s">
         <v>20</v>
       </c>
@@ -1368,10 +2072,10 @@
         <v>22</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
@@ -1380,7 +2084,9 @@
       <c r="J20" s="3"/>
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
-      <c r="M20" s="3"/>
+      <c r="M20" s="3">
+        <v>22</v>
+      </c>
       <c r="N20" s="3"/>
       <c r="O20" s="3"/>
       <c r="P20" s="3"/>
@@ -1388,30 +2094,34 @@
       <c r="R20" s="3"/>
       <c r="S20" s="3"/>
     </row>
-    <row r="21" spans="1:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C21" s="2" t="s">
+    <row r="21" spans="1:19" ht="17.250000">
+      <c r="A21" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="F21" s="3"/>
+      <c r="D21" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="E21" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="F21" s="3">
+        <v>7</v>
+      </c>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
-      <c r="M21" s="3"/>
+      <c r="M21" s="3">
+        <v>17</v>
+      </c>
       <c r="N21" s="3"/>
       <c r="O21" s="3"/>
       <c r="P21" s="3"/>
@@ -1419,21 +2129,21 @@
       <c r="R21" s="3"/>
       <c r="S21" s="3"/>
     </row>
-    <row r="22" spans="1:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>20</v>
-      </c>
-      <c r="B22" t="s">
-        <v>21</v>
-      </c>
-      <c r="C22" t="s">
+    <row r="22" spans="1:19" ht="17.250000">
+      <c r="A22" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="D22" t="s">
-        <v>64</v>
-      </c>
-      <c r="E22" t="s">
-        <v>65</v>
+      <c r="D22" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="E22" s="0" t="s">
+        <v>67</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
@@ -1442,7 +2152,9 @@
       <c r="J22" s="3"/>
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
-      <c r="M22" s="3"/>
+      <c r="M22" s="3">
+        <v>25</v>
+      </c>
       <c r="N22" s="3"/>
       <c r="O22" s="3"/>
       <c r="P22" s="3"/>
@@ -1450,21 +2162,21 @@
       <c r="R22" s="3"/>
       <c r="S22" s="3"/>
     </row>
-    <row r="23" spans="1:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>20</v>
-      </c>
-      <c r="B23" t="s">
-        <v>21</v>
-      </c>
-      <c r="C23" t="s">
+    <row r="23" spans="1:19" ht="17.250000">
+      <c r="A23" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="B23" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C23" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="D23" t="s">
-        <v>66</v>
-      </c>
-      <c r="E23" t="s">
-        <v>67</v>
+      <c r="D23" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="E23" s="0" t="s">
+        <v>69</v>
       </c>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
@@ -1473,7 +2185,9 @@
       <c r="J23" s="3"/>
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
-      <c r="M23" s="3"/>
+      <c r="M23" s="3">
+        <v>21</v>
+      </c>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
       <c r="P23" s="3"/>
@@ -1481,52 +2195,58 @@
       <c r="R23" s="3"/>
       <c r="S23" s="3"/>
     </row>
-    <row r="24" spans="1:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>20</v>
-      </c>
-      <c r="B24" t="s">
-        <v>21</v>
-      </c>
-      <c r="C24" t="s">
+    <row r="24" spans="1:19" ht="17.250000">
+      <c r="A24" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C24" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="D24" t="s">
-        <v>68</v>
-      </c>
-      <c r="E24" t="s">
-        <v>69</v>
-      </c>
-      <c r="F24" s="3"/>
+      <c r="D24" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="E24" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="F24" s="3">
+        <v>23</v>
+      </c>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
-      <c r="M24" s="3"/>
-      <c r="N24" s="3"/>
+      <c r="M24" s="3">
+        <v>20</v>
+      </c>
+      <c r="N24" s="3">
+        <v>24</v>
+      </c>
       <c r="O24" s="3"/>
       <c r="P24" s="3"/>
       <c r="Q24" s="3"/>
       <c r="R24" s="3"/>
       <c r="S24" s="3"/>
     </row>
-    <row r="25" spans="1:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>20</v>
-      </c>
-      <c r="B25" t="s">
-        <v>21</v>
-      </c>
-      <c r="C25" t="s">
+    <row r="25" spans="1:19" ht="17.250000">
+      <c r="A25" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="B25" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C25" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="D25" t="s">
-        <v>70</v>
-      </c>
-      <c r="E25" t="s">
-        <v>71</v>
+      <c r="D25" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="E25" s="0" t="s">
+        <v>73</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
@@ -1535,7 +2255,9 @@
       <c r="J25" s="3"/>
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
-      <c r="M25" s="3"/>
+      <c r="M25" s="3">
+        <v>24</v>
+      </c>
       <c r="N25" s="3"/>
       <c r="O25" s="3"/>
       <c r="P25" s="3"/>
@@ -1543,21 +2265,21 @@
       <c r="R25" s="3"/>
       <c r="S25" s="3"/>
     </row>
-    <row r="26" spans="1:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>20</v>
-      </c>
-      <c r="B26" t="s">
-        <v>21</v>
-      </c>
-      <c r="C26" t="s">
+    <row r="26" spans="1:19" ht="17.250000">
+      <c r="A26" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="B26" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C26" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="D26" t="s">
-        <v>72</v>
-      </c>
-      <c r="E26" t="s">
-        <v>73</v>
+      <c r="D26" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="E26" s="0" t="s">
+        <v>26</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
@@ -1566,7 +2288,9 @@
       <c r="J26" s="3"/>
       <c r="K26" s="3"/>
       <c r="L26" s="3"/>
-      <c r="M26" s="3"/>
+      <c r="M26" s="3">
+        <v>26</v>
+      </c>
       <c r="N26" s="3"/>
       <c r="O26" s="3"/>
       <c r="P26" s="3"/>
@@ -1574,52 +2298,58 @@
       <c r="R26" s="3"/>
       <c r="S26" s="3"/>
     </row>
-    <row r="27" spans="1:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>20</v>
-      </c>
-      <c r="B27" t="s">
-        <v>21</v>
-      </c>
-      <c r="C27" t="s">
-        <v>22</v>
-      </c>
-      <c r="D27" t="s">
-        <v>74</v>
-      </c>
-      <c r="E27" t="s">
+    <row r="27" spans="1:19" ht="17.250000">
+      <c r="A27" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="B27" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C27" s="0" t="s">
+        <v>75</v>
+      </c>
+      <c r="D27" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="E27" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="F27" s="3">
         <v>26</v>
       </c>
-      <c r="F27" s="3"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
       <c r="J27" s="3"/>
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
-      <c r="M27" s="3"/>
-      <c r="N27" s="3"/>
+      <c r="M27" s="3">
+        <v>26</v>
+      </c>
+      <c r="N27" s="3">
+        <v>30</v>
+      </c>
       <c r="O27" s="3"/>
       <c r="P27" s="3"/>
       <c r="Q27" s="3"/>
       <c r="R27" s="3"/>
       <c r="S27" s="3"/>
     </row>
-    <row r="28" spans="1:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>20</v>
-      </c>
-      <c r="B28" t="s">
-        <v>21</v>
-      </c>
-      <c r="C28" t="s">
-        <v>75</v>
-      </c>
-      <c r="D28" t="s">
-        <v>76</v>
-      </c>
-      <c r="E28" t="s">
-        <v>77</v>
+    <row r="28" spans="1:19" ht="17.250000">
+      <c r="A28" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="B28" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="C28" s="0" t="s">
+        <v>78</v>
+      </c>
+      <c r="D28" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="E28" s="0" t="s">
+        <v>80</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
@@ -1628,7 +2358,9 @@
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
-      <c r="M28" s="3"/>
+      <c r="M28" s="3">
+        <v>21</v>
+      </c>
       <c r="N28" s="3"/>
       <c r="O28" s="3"/>
       <c r="P28" s="3"/>
@@ -1636,92 +2368,110 @@
       <c r="R28" s="3"/>
       <c r="S28" s="3"/>
     </row>
-    <row r="29" spans="1:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>20</v>
-      </c>
-      <c r="B29" t="s">
-        <v>5</v>
-      </c>
-      <c r="C29" t="s">
-        <v>78</v>
-      </c>
-      <c r="D29" t="s">
-        <v>79</v>
-      </c>
-      <c r="E29" t="s">
-        <v>80</v>
-      </c>
-      <c r="F29" s="3"/>
+    <row r="29" spans="1:19" ht="17.250000">
+      <c r="A29" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="B29" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C29" s="0" t="s">
+        <v>81</v>
+      </c>
+      <c r="D29" s="0" t="s">
+        <v>82</v>
+      </c>
+      <c r="E29" s="0" t="s">
+        <v>83</v>
+      </c>
+      <c r="F29" s="3">
+        <v>26</v>
+      </c>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
-      <c r="M29" s="3"/>
-      <c r="N29" s="3"/>
-      <c r="O29" s="3"/>
+      <c r="M29" s="3">
+        <v>25</v>
+      </c>
+      <c r="N29" s="3">
+        <v>27</v>
+      </c>
+      <c r="O29" s="3">
+        <v>29</v>
+      </c>
       <c r="P29" s="3"/>
       <c r="Q29" s="3"/>
       <c r="R29" s="3"/>
       <c r="S29" s="3"/>
     </row>
-    <row r="30" spans="1:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>20</v>
-      </c>
-      <c r="B30" t="s">
-        <v>21</v>
-      </c>
-      <c r="C30" t="s">
-        <v>81</v>
-      </c>
-      <c r="D30" t="s">
-        <v>82</v>
-      </c>
-      <c r="E30" t="s">
-        <v>83</v>
-      </c>
-      <c r="F30" s="3"/>
+    <row r="30" spans="1:19" ht="17.250000">
+      <c r="A30" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="B30" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C30" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="D30" s="0" t="s">
+        <v>85</v>
+      </c>
+      <c r="E30" s="0" t="s">
+        <v>86</v>
+      </c>
+      <c r="F30" s="3">
+        <v>23</v>
+      </c>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
       <c r="K30" s="3"/>
       <c r="L30" s="3"/>
-      <c r="M30" s="3"/>
-      <c r="N30" s="3"/>
+      <c r="M30" s="3">
+        <v>22</v>
+      </c>
+      <c r="N30" s="3">
+        <v>24</v>
+      </c>
       <c r="O30" s="3"/>
       <c r="P30" s="3"/>
       <c r="Q30" s="3"/>
       <c r="R30" s="3"/>
       <c r="S30" s="3"/>
     </row>
-    <row r="31" spans="1:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>20</v>
-      </c>
-      <c r="B31" t="s">
-        <v>21</v>
-      </c>
-      <c r="C31" t="s">
-        <v>84</v>
-      </c>
-      <c r="D31" t="s">
-        <v>85</v>
-      </c>
-      <c r="E31" t="s">
-        <v>86</v>
-      </c>
-      <c r="F31" s="3"/>
+    <row r="31" spans="1:19" ht="17.250000">
+      <c r="A31" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="B31" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C31" s="0" t="s">
+        <v>87</v>
+      </c>
+      <c r="D31" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="E31" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="F31" s="3">
+        <v>24</v>
+      </c>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
       <c r="K31" s="3"/>
       <c r="L31" s="3"/>
-      <c r="M31" s="3"/>
+      <c r="M31" s="3">
+        <v>25</v>
+      </c>
       <c r="N31" s="3"/>
       <c r="O31" s="3"/>
       <c r="P31" s="3"/>
@@ -1729,39 +2479,25 @@
       <c r="R31" s="3"/>
       <c r="S31" s="3"/>
     </row>
-    <row r="32" spans="1:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>20</v>
-      </c>
-      <c r="B32" t="s">
-        <v>21</v>
-      </c>
-      <c r="C32" t="s">
-        <v>87</v>
-      </c>
-      <c r="D32" t="s">
-        <v>88</v>
-      </c>
-      <c r="E32" t="s">
-        <v>55</v>
-      </c>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
-      <c r="J32" s="3"/>
-      <c r="K32" s="3"/>
-      <c r="L32" s="3"/>
-      <c r="M32" s="3"/>
-      <c r="N32" s="3"/>
-      <c r="O32" s="3"/>
-      <c r="P32" s="3"/>
-      <c r="Q32" s="3"/>
-      <c r="R32" s="3"/>
-      <c r="S32" s="3"/>
+    <row r="32" spans="1:19">
+      <c r="F32" s="0"/>
+      <c r="G32" s="0"/>
+      <c r="H32" s="0"/>
+      <c r="I32" s="0"/>
+      <c r="J32" s="0"/>
+      <c r="K32" s="0"/>
+      <c r="L32" s="0"/>
+      <c r="M32" s="0"/>
+      <c r="N32" s="0"/>
+      <c r="O32" s="0"/>
+      <c r="P32" s="0"/>
+      <c r="Q32" s="0"/>
+      <c r="R32" s="0"/>
+      <c r="S32" s="0"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.70" right="0.70" top="0.75" bottom="0.75" header="0.30" footer="0.30"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>